--- a/public/sap-reporting/expansion-150-downloads/EXT-PM04-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-PM04-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rea0a95335ca94c18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rf22ada15651241be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rff441c617a614223"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R8b4660462ffb4b84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R8a861e9266864985"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R1ff67eb09ab648d4"/>
   </x:sheets>
 </x:workbook>
 </file>
